--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-25).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-25).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-185</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>R$ 958.279,05</t>
-  </si>
-  <si>
-    <t>R$ 4.914,25
-R$ 4.999,67</t>
-  </si>
-  <si>
-    <t>(8.4%)
-(6.8%)</t>
-  </si>
-  <si>
-    <t>50.8</t>
-  </si>
-  <si>
-    <t>(14.8%)</t>
-  </si>
-  <si>
-    <t>112.0%</t>
-  </si>
-  <si>
-    <t>71.0%</t>
+187</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>R$ 963.617,75</t>
+  </si>
+  <si>
+    <t>R$ 4.891,46
+R$ 4.974,75</t>
+  </si>
+  <si>
+    <t>(8.2%)
+(6.7%)</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>(14.7%)</t>
+  </si>
+  <si>
+    <t>111.5%</t>
+  </si>
+  <si>
+    <t>70.5%</t>
   </si>
   <si>
     <t>3.6%</t>
@@ -950,10 +950,10 @@
     <t>26.1</t>
   </si>
   <si>
-    <t>76.0%</t>
-  </si>
-  <si>
-    <t>7.8%</t>
+    <t>76.1%</t>
+  </si>
+  <si>
+    <t>8.0%</t>
   </si>
   <si>
     <t>5.1</t>
@@ -962,19 +962,19 @@
     <t>6.1</t>
   </si>
   <si>
-    <t>11.3</t>
+    <t>11.4</t>
   </si>
   <si>
     <t>18.0</t>
   </si>
   <si>
-    <t>74.3%</t>
+    <t>74.2%</t>
   </si>
   <si>
     <t>-R$ 26.027,65</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -5992,7 +5992,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -6028,25 +6028,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>4294</v>
+      </c>
+      <c r="P36" s="5">
+        <v>4294</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.90218835828829613</v>
+      </c>
+      <c r="R36" s="7">
+        <v>44</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.76000000000000001</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.33947815556590594</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.024196739636702377</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.056256986492780624</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.00968735444806707</v>
+      </c>
+      <c r="X36" s="8">
+        <v>32.471353125</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.28125</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>6.4336812500000002</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>9.2489258064516129</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>15.990069</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>22.475521874999998</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7913,7 +7949,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7949,25 +7985,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1044.7</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1044.7</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.51234654343462638</v>
+      </c>
+      <c r="R51" s="7">
+        <v>10</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.54545454545454541</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0.044452953000861488</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.31458791997702684</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.0214540059347181</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.10107877859672633</v>
+      </c>
+      <c r="X51" s="8">
+        <v>38.495825000000004</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>5.3650000000000002</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>18.916675000000001</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>25.337499000000001</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>32.241675000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.25</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12672,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -16857,7 +16929,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17119,7 +17191,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17512,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18689,7 +18761,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18820,7 +18892,7 @@
         <v>0</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -21003,7 +21075,7 @@
         <v>-307.63</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21130,7 +21202,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22287,7 +22359,7 @@
         <v>0</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -28454,7 +28526,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
